--- a/output/Hunan/郴州市_news.xlsx
+++ b/output/Hunan/郴州市_news.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5116" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5117" uniqueCount="960">
   <si>
     <t>location</t>
   </si>
@@ -2935,18 +2935,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3404,28 +3404,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3549,11 +3549,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3988,7 +3989,7 @@
         <v>23</v>
       </c>
       <c r="L2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M2">
         <v>7</v>
@@ -4038,7 +4039,7 @@
         <v>23</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -4088,7 +4089,7 @@
         <v>23</v>
       </c>
       <c r="L4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -4138,7 +4139,7 @@
         <v>23</v>
       </c>
       <c r="L5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -4188,7 +4189,7 @@
         <v>44</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -4196,7 +4197,7 @@
       <c r="N6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="P6" t="s">
@@ -4238,7 +4239,7 @@
         <v>23</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -4288,7 +4289,7 @@
         <v>23</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -4388,7 +4389,7 @@
         <v>23</v>
       </c>
       <c r="L10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -4438,7 +4439,7 @@
         <v>23</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -4488,7 +4489,7 @@
         <v>23</v>
       </c>
       <c r="L12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -4538,7 +4539,7 @@
         <v>23</v>
       </c>
       <c r="L13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -4588,7 +4589,7 @@
         <v>23</v>
       </c>
       <c r="L14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -4638,7 +4639,7 @@
         <v>23</v>
       </c>
       <c r="L15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -4688,7 +4689,7 @@
         <v>23</v>
       </c>
       <c r="L16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -4738,7 +4739,7 @@
         <v>23</v>
       </c>
       <c r="L17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -4788,7 +4789,7 @@
         <v>23</v>
       </c>
       <c r="L18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -4838,7 +4839,7 @@
         <v>23</v>
       </c>
       <c r="L19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -4888,7 +4889,7 @@
         <v>23</v>
       </c>
       <c r="L20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -4938,7 +4939,7 @@
         <v>23</v>
       </c>
       <c r="L21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -4988,7 +4989,7 @@
         <v>23</v>
       </c>
       <c r="L22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -5038,7 +5039,7 @@
         <v>23</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -5088,7 +5089,7 @@
         <v>99</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -5138,7 +5139,7 @@
         <v>103</v>
       </c>
       <c r="L25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25">
         <v>5</v>
@@ -5188,7 +5189,7 @@
         <v>23</v>
       </c>
       <c r="L26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -5238,7 +5239,7 @@
         <v>23</v>
       </c>
       <c r="L27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -5288,7 +5289,7 @@
         <v>23</v>
       </c>
       <c r="L28">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -5338,7 +5339,7 @@
         <v>23</v>
       </c>
       <c r="L29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -5388,7 +5389,7 @@
         <v>23</v>
       </c>
       <c r="L30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -5438,7 +5439,7 @@
         <v>23</v>
       </c>
       <c r="L31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -5488,7 +5489,7 @@
         <v>121</v>
       </c>
       <c r="L32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -5538,7 +5539,7 @@
         <v>127</v>
       </c>
       <c r="L33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -5588,7 +5589,7 @@
         <v>23</v>
       </c>
       <c r="L34">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -5638,7 +5639,7 @@
         <v>23</v>
       </c>
       <c r="L35">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M35">
         <v>6</v>
@@ -5688,7 +5689,7 @@
         <v>23</v>
       </c>
       <c r="L36">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -5738,7 +5739,7 @@
         <v>23</v>
       </c>
       <c r="L37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -5788,7 +5789,7 @@
         <v>23</v>
       </c>
       <c r="L38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>1</v>
@@ -5838,7 +5839,7 @@
         <v>23</v>
       </c>
       <c r="L39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -5888,7 +5889,7 @@
         <v>23</v>
       </c>
       <c r="L40">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -5938,7 +5939,7 @@
         <v>127</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -5988,7 +5989,7 @@
         <v>151</v>
       </c>
       <c r="L42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M42">
         <v>5</v>
@@ -6238,7 +6239,7 @@
         <v>23</v>
       </c>
       <c r="L47">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -7438,7 +7439,7 @@
         <v>23</v>
       </c>
       <c r="L71">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M71">
         <v>6</v>
@@ -7488,7 +7489,7 @@
         <v>23</v>
       </c>
       <c r="L72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M72">
         <v>6</v>
@@ -7788,7 +7789,7 @@
         <v>23</v>
       </c>
       <c r="L78">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M78">
         <v>6</v>
@@ -7888,7 +7889,7 @@
         <v>23</v>
       </c>
       <c r="L80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M80">
         <v>1</v>
@@ -8088,7 +8089,7 @@
         <v>23</v>
       </c>
       <c r="L84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M84">
         <v>5</v>
@@ -8388,7 +8389,7 @@
         <v>23</v>
       </c>
       <c r="L90">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M90">
         <v>7</v>
@@ -9538,7 +9539,7 @@
         <v>23</v>
       </c>
       <c r="L113">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M113">
         <v>5</v>
@@ -11388,7 +11389,7 @@
         <v>320</v>
       </c>
       <c r="L150">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M150">
         <v>5</v>
@@ -12538,7 +12539,7 @@
         <v>23</v>
       </c>
       <c r="L173">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M173">
         <v>1</v>
@@ -15088,7 +15089,7 @@
         <v>23</v>
       </c>
       <c r="L224">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M224">
         <v>7</v>
@@ -19988,7 +19989,7 @@
         <v>23</v>
       </c>
       <c r="L322">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M322">
         <v>5</v>
@@ -20038,7 +20039,7 @@
         <v>320</v>
       </c>
       <c r="L323">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M323">
         <v>5</v>
@@ -20088,7 +20089,7 @@
         <v>320</v>
       </c>
       <c r="L324">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M324">
         <v>5</v>
@@ -20138,7 +20139,7 @@
         <v>23</v>
       </c>
       <c r="L325">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M325">
         <v>5</v>
@@ -20188,7 +20189,7 @@
         <v>23</v>
       </c>
       <c r="L326">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M326">
         <v>5</v>
@@ -20238,7 +20239,7 @@
         <v>23</v>
       </c>
       <c r="L327">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M327">
         <v>5</v>
@@ -20288,7 +20289,7 @@
         <v>23</v>
       </c>
       <c r="L328">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M328">
         <v>5</v>
@@ -20338,7 +20339,7 @@
         <v>23</v>
       </c>
       <c r="L329">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M329">
         <v>5</v>
@@ -20388,7 +20389,7 @@
         <v>23</v>
       </c>
       <c r="L330">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M330">
         <v>5</v>
@@ -20438,7 +20439,7 @@
         <v>23</v>
       </c>
       <c r="L331">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M331">
         <v>5</v>
@@ -20488,7 +20489,7 @@
         <v>23</v>
       </c>
       <c r="L332">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M332">
         <v>5</v>
@@ -20538,7 +20539,7 @@
         <v>23</v>
       </c>
       <c r="L333">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M333">
         <v>5</v>
@@ -20588,7 +20589,7 @@
         <v>23</v>
       </c>
       <c r="L334">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M334">
         <v>5</v>
@@ -20638,7 +20639,7 @@
         <v>23</v>
       </c>
       <c r="L335">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M335">
         <v>5</v>
@@ -20688,7 +20689,7 @@
         <v>23</v>
       </c>
       <c r="L336">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M336">
         <v>5</v>
@@ -20738,7 +20739,7 @@
         <v>23</v>
       </c>
       <c r="L337">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M337">
         <v>5</v>
@@ -20788,7 +20789,7 @@
         <v>23</v>
       </c>
       <c r="L338">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M338">
         <v>5</v>
@@ -20838,7 +20839,7 @@
         <v>771</v>
       </c>
       <c r="L339">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M339">
         <v>5</v>
@@ -20888,7 +20889,7 @@
         <v>23</v>
       </c>
       <c r="L340">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M340">
         <v>5</v>
@@ -20938,7 +20939,7 @@
         <v>23</v>
       </c>
       <c r="L341">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M341">
         <v>5</v>
@@ -20988,7 +20989,7 @@
         <v>23</v>
       </c>
       <c r="L342">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M342">
         <v>5</v>
@@ -21038,7 +21039,7 @@
         <v>23</v>
       </c>
       <c r="L343">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M343">
         <v>5</v>
@@ -21088,13 +21089,13 @@
         <v>23</v>
       </c>
       <c r="L344">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M344">
         <v>1</v>
       </c>
-      <c r="N344">
-        <v>0</v>
+      <c r="N344" t="s">
+        <v>52</v>
       </c>
       <c r="O344" t="s">
         <v>785</v>
@@ -21138,7 +21139,7 @@
         <v>23</v>
       </c>
       <c r="L345">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M345">
         <v>1</v>
@@ -21188,7 +21189,7 @@
         <v>23</v>
       </c>
       <c r="L346">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M346">
         <v>5</v>
@@ -21238,7 +21239,7 @@
         <v>23</v>
       </c>
       <c r="L347">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M347">
         <v>5</v>
@@ -21288,7 +21289,7 @@
         <v>23</v>
       </c>
       <c r="L348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M348">
         <v>5</v>
@@ -21338,7 +21339,7 @@
         <v>320</v>
       </c>
       <c r="L349">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M349">
         <v>5</v>
@@ -21388,7 +21389,7 @@
         <v>23</v>
       </c>
       <c r="L350">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M350">
         <v>5</v>
@@ -21438,7 +21439,7 @@
         <v>23</v>
       </c>
       <c r="L351">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M351">
         <v>5</v>
@@ -21488,7 +21489,7 @@
         <v>23</v>
       </c>
       <c r="L352">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M352">
         <v>5</v>
@@ -21538,7 +21539,7 @@
         <v>23</v>
       </c>
       <c r="L353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M353">
         <v>5</v>
@@ -21588,7 +21589,7 @@
         <v>320</v>
       </c>
       <c r="L354">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M354">
         <v>5</v>
@@ -21638,7 +21639,7 @@
         <v>807</v>
       </c>
       <c r="L355">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M355">
         <v>5</v>
@@ -21688,7 +21689,7 @@
         <v>23</v>
       </c>
       <c r="L356">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M356">
         <v>5</v>
@@ -21738,7 +21739,7 @@
         <v>23</v>
       </c>
       <c r="L357">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M357">
         <v>5</v>
@@ -21788,7 +21789,7 @@
         <v>23</v>
       </c>
       <c r="L358">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M358">
         <v>5</v>
@@ -21838,7 +21839,7 @@
         <v>23</v>
       </c>
       <c r="L359">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M359">
         <v>2</v>
@@ -21888,7 +21889,7 @@
         <v>23</v>
       </c>
       <c r="L360">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M360">
         <v>5</v>
@@ -21938,7 +21939,7 @@
         <v>23</v>
       </c>
       <c r="L361">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M361">
         <v>5</v>
@@ -21988,7 +21989,7 @@
         <v>23</v>
       </c>
       <c r="L362">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M362">
         <v>5</v>
@@ -22038,7 +22039,7 @@
         <v>23</v>
       </c>
       <c r="L363">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M363">
         <v>5</v>
@@ -22088,7 +22089,7 @@
         <v>23</v>
       </c>
       <c r="L364">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M364">
         <v>5</v>
@@ -22138,7 +22139,7 @@
         <v>23</v>
       </c>
       <c r="L365">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M365">
         <v>5</v>
@@ -22188,7 +22189,7 @@
         <v>23</v>
       </c>
       <c r="L366">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M366">
         <v>5</v>
@@ -22238,7 +22239,7 @@
         <v>23</v>
       </c>
       <c r="L367">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M367">
         <v>5</v>
@@ -22288,7 +22289,7 @@
         <v>23</v>
       </c>
       <c r="L368">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M368">
         <v>5</v>
@@ -22338,7 +22339,7 @@
         <v>23</v>
       </c>
       <c r="L369">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M369">
         <v>5</v>
@@ -22388,7 +22389,7 @@
         <v>23</v>
       </c>
       <c r="L370">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M370">
         <v>5</v>
@@ -22438,7 +22439,7 @@
         <v>23</v>
       </c>
       <c r="L371">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M371">
         <v>5</v>
@@ -22488,7 +22489,7 @@
         <v>23</v>
       </c>
       <c r="L372">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M372">
         <v>5</v>
@@ -22538,7 +22539,7 @@
         <v>23</v>
       </c>
       <c r="L373">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M373">
         <v>5</v>
@@ -22588,7 +22589,7 @@
         <v>23</v>
       </c>
       <c r="L374">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M374">
         <v>5</v>
@@ -22638,7 +22639,7 @@
         <v>23</v>
       </c>
       <c r="L375">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M375">
         <v>5</v>
@@ -22688,7 +22689,7 @@
         <v>23</v>
       </c>
       <c r="L376">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M376">
         <v>8</v>
@@ -22738,7 +22739,7 @@
         <v>23</v>
       </c>
       <c r="L377">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M377">
         <v>5</v>
@@ -22788,7 +22789,7 @@
         <v>23</v>
       </c>
       <c r="L378">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M378">
         <v>8</v>
@@ -22838,7 +22839,7 @@
         <v>23</v>
       </c>
       <c r="L379">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M379">
         <v>5</v>
@@ -22888,7 +22889,7 @@
         <v>23</v>
       </c>
       <c r="L380">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M380">
         <v>2</v>
@@ -22938,7 +22939,7 @@
         <v>23</v>
       </c>
       <c r="L381">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M381">
         <v>2</v>
@@ -22988,7 +22989,7 @@
         <v>23</v>
       </c>
       <c r="L382">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M382">
         <v>5</v>
@@ -23038,7 +23039,7 @@
         <v>23</v>
       </c>
       <c r="L383">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M383">
         <v>1</v>
@@ -23088,7 +23089,7 @@
         <v>23</v>
       </c>
       <c r="L384">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M384">
         <v>1</v>
@@ -23138,7 +23139,7 @@
         <v>23</v>
       </c>
       <c r="L385">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M385">
         <v>1</v>
@@ -23188,7 +23189,7 @@
         <v>23</v>
       </c>
       <c r="L386">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M386">
         <v>2</v>
@@ -23238,7 +23239,7 @@
         <v>23</v>
       </c>
       <c r="L387">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M387">
         <v>2</v>
@@ -23288,7 +23289,7 @@
         <v>23</v>
       </c>
       <c r="L388">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M388">
         <v>5</v>
@@ -23338,7 +23339,7 @@
         <v>23</v>
       </c>
       <c r="L389">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M389">
         <v>3</v>
@@ -23388,7 +23389,7 @@
         <v>23</v>
       </c>
       <c r="L390">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M390">
         <v>5</v>
@@ -23438,7 +23439,7 @@
         <v>23</v>
       </c>
       <c r="L391">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M391">
         <v>5</v>
@@ -23488,7 +23489,7 @@
         <v>23</v>
       </c>
       <c r="L392">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M392">
         <v>5</v>
@@ -23538,7 +23539,7 @@
         <v>23</v>
       </c>
       <c r="L393">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M393">
         <v>5</v>
@@ -23588,7 +23589,7 @@
         <v>23</v>
       </c>
       <c r="L394">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M394">
         <v>5</v>
@@ -23638,7 +23639,7 @@
         <v>23</v>
       </c>
       <c r="L395">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M395">
         <v>5</v>
@@ -23688,7 +23689,7 @@
         <v>23</v>
       </c>
       <c r="L396">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M396">
         <v>5</v>
@@ -23738,7 +23739,7 @@
         <v>44</v>
       </c>
       <c r="L397">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M397">
         <v>5</v>
@@ -23788,7 +23789,7 @@
         <v>23</v>
       </c>
       <c r="L398">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M398">
         <v>5</v>
@@ -23838,7 +23839,7 @@
         <v>23</v>
       </c>
       <c r="L399">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M399">
         <v>5</v>
@@ -23888,7 +23889,7 @@
         <v>121</v>
       </c>
       <c r="L400">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M400">
         <v>5</v>
@@ -23938,7 +23939,7 @@
         <v>23</v>
       </c>
       <c r="L401">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M401">
         <v>5</v>
@@ -23988,7 +23989,7 @@
         <v>23</v>
       </c>
       <c r="L402">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M402">
         <v>5</v>
@@ -24038,7 +24039,7 @@
         <v>23</v>
       </c>
       <c r="L403">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M403">
         <v>5</v>
@@ -24088,7 +24089,7 @@
         <v>23</v>
       </c>
       <c r="L404">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M404">
         <v>5</v>
@@ -24138,7 +24139,7 @@
         <v>23</v>
       </c>
       <c r="L405">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M405">
         <v>5</v>
@@ -24188,7 +24189,7 @@
         <v>23</v>
       </c>
       <c r="L406">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M406">
         <v>1</v>
@@ -24238,7 +24239,7 @@
         <v>23</v>
       </c>
       <c r="L407">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M407">
         <v>5</v>
@@ -24288,7 +24289,7 @@
         <v>23</v>
       </c>
       <c r="L408">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M408">
         <v>5</v>
@@ -24338,7 +24339,7 @@
         <v>23</v>
       </c>
       <c r="L409">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M409">
         <v>5</v>
@@ -24388,7 +24389,7 @@
         <v>23</v>
       </c>
       <c r="L410">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M410">
         <v>5</v>
@@ -24438,7 +24439,7 @@
         <v>23</v>
       </c>
       <c r="L411">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M411">
         <v>1</v>
@@ -24488,7 +24489,7 @@
         <v>23</v>
       </c>
       <c r="L412">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M412">
         <v>1</v>
@@ -24538,7 +24539,7 @@
         <v>23</v>
       </c>
       <c r="L413">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M413">
         <v>1</v>
@@ -24588,7 +24589,7 @@
         <v>23</v>
       </c>
       <c r="L414">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M414">
         <v>4</v>
@@ -24638,7 +24639,7 @@
         <v>23</v>
       </c>
       <c r="L415">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M415">
         <v>1</v>
@@ -24688,7 +24689,7 @@
         <v>23</v>
       </c>
       <c r="L416">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M416">
         <v>5</v>
@@ -24738,7 +24739,7 @@
         <v>23</v>
       </c>
       <c r="L417">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M417">
         <v>5</v>
@@ -24788,7 +24789,7 @@
         <v>121</v>
       </c>
       <c r="L418">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M418">
         <v>5</v>
@@ -24838,7 +24839,7 @@
         <v>23</v>
       </c>
       <c r="L419">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M419">
         <v>5</v>
@@ -24888,7 +24889,7 @@
         <v>23</v>
       </c>
       <c r="L420">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M420">
         <v>5</v>
@@ -24938,7 +24939,7 @@
         <v>23</v>
       </c>
       <c r="L421">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M421">
         <v>1</v>
@@ -24988,7 +24989,7 @@
         <v>23</v>
       </c>
       <c r="L422">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M422">
         <v>5</v>
@@ -25038,7 +25039,7 @@
         <v>23</v>
       </c>
       <c r="L423">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M423">
         <v>3</v>
@@ -25088,7 +25089,7 @@
         <v>23</v>
       </c>
       <c r="L424">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M424">
         <v>16</v>
@@ -25138,7 +25139,7 @@
         <v>23</v>
       </c>
       <c r="L425">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M425">
         <v>1</v>
@@ -25188,7 +25189,7 @@
         <v>23</v>
       </c>
       <c r="L426">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M426">
         <v>5</v>
@@ -25204,6 +25205,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O6" r:id="rId1" display="http://113.219.136.14:36001/data/dataSet/toDataDetails/30702198010900002000011/010950"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
